--- a/3. FOTOCOLORIMETRIA Y ESPECTROMETRIA/relacion_volumenes_relacion_determinacion_NEULOG.xlsx
+++ b/3. FOTOCOLORIMETRIA Y ESPECTROMETRIA/relacion_volumenes_relacion_determinacion_NEULOG.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bremdows\UNSAAC\SEMESTRE X\LABORATORIO DE BIOINGENIERIA\lab-bioingenieria\3. FOTOCOLORIMETRIA Y ESPECTROMETRIA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UNSAAC\SEMESTRE X\LABORATORIO DE BIOINGENIERIA\lab-bioingenieria\3. FOTOCOLORIMETRIA Y ESPECTROMETRIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8638895F-D180-4FD6-9163-B2D1149469AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6A7C6E3-BA44-4507-953D-2195C8313223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="348" windowWidth="23256" windowHeight="12720" xr2:uid="{AD216724-D09A-4721-95A5-738CB4CA3C8B}"/>
+    <workbookView xWindow="810" yWindow="-120" windowWidth="28110" windowHeight="16440" activeTab="1" xr2:uid="{AD216724-D09A-4721-95A5-738CB4CA3C8B}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
-    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
-    <sheet name="Hoja3" sheetId="3" r:id="rId3"/>
+    <sheet name="Azul" sheetId="1" r:id="rId1"/>
+    <sheet name="Verde" sheetId="2" r:id="rId2"/>
+    <sheet name="Azul v2" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,8 +29,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -38,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="2">
   <si>
     <t>A</t>
   </si>
@@ -50,8 +48,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -79,8 +85,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -113,6 +123,52 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+              <a:lnSpc>
+                <a:spcPct val="100000"/>
+              </a:lnSpc>
+              <a:spcBef>
+                <a:spcPts val="0"/>
+              </a:spcBef>
+              <a:spcAft>
+                <a:spcPts val="0"/>
+              </a:spcAft>
+              <a:buClrTx/>
+              <a:buSzTx/>
+              <a:buFontTx/>
+              <a:buNone/>
+              <a:tabLst/>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Absorbancia  vs concentración</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -125,13 +181,27 @@
         <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
         <a:lstStyle/>
         <a:p>
-          <a:pPr>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
             <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
+                <a:sysClr val="windowText" lastClr="000000">
                   <a:lumMod val="65000"/>
                   <a:lumOff val="35000"/>
-                </a:schemeClr>
+                </a:sysClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -151,6 +221,17 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Azul!$L$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>A</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
@@ -185,11 +266,44 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:trendlineType val="poly"/>
-            <c:order val="2"/>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
             <c:dispRSqr val="1"/>
             <c:dispEq val="1"/>
             <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.15957422999768009"/>
+                  <c:y val="-5.1676702176933764E-2"/>
+                </c:manualLayout>
+              </c:layout>
               <c:numFmt formatCode="General" sourceLinked="0"/>
               <c:spPr>
                 <a:noFill/>
@@ -222,7 +336,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Hoja1!$A$2:$A$6</c:f>
+              <c:f>Azul!$K$2:$K$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -246,7 +360,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Hoja1!$B$2:$B$6</c:f>
+              <c:f>Azul!$L$2:$L$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -271,7 +385,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-D749-40AD-882D-1B290E821B3A}"/>
+              <c16:uniqueId val="{00000000-B034-4A94-A9F6-CF281C901918}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -283,11 +397,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1850114863"/>
-        <c:axId val="1850115343"/>
+        <c:axId val="957396735"/>
+        <c:axId val="957393855"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1850114863"/>
+        <c:axId val="957396735"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -344,12 +458,12 @@
             <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1850115343"/>
+        <c:crossAx val="957393855"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1850115343"/>
+        <c:axId val="957393855"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -406,7 +520,7 @@
             <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1850114863"/>
+        <c:crossAx val="957396735"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -420,6 +534,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -427,7 +542,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -462,7 +576,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="es-ES"/>
@@ -477,6 +591,38 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-PE" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Concentración vs Absorbancia</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -515,6 +661,17 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Azul v2'!$K$27</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Concentración</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
@@ -553,9 +710,83 @@
             <c:dispRSqr val="0"/>
             <c:dispEq val="0"/>
           </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.15934802882376647"/>
+                  <c:y val="3.6598425196850394E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="es-PE"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Hoja2!$A$2:$A$6</c:f>
+              <c:f>'Azul v2'!$J$28:$J$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.56000000000000005</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.24</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.97</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.52</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Azul v2'!$K$28:$K$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -576,35 +807,11 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Hoja2!$B$2:$B$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>0.61</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.1100000000000001</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.68</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.83</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1.94</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-42B5-4975-BA5E-48027DA87558}"/>
+              <c16:uniqueId val="{00000000-9BAC-4275-8861-544713C57B99}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -616,11 +823,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1920220447"/>
-        <c:axId val="1920225727"/>
+        <c:axId val="915913423"/>
+        <c:axId val="915933583"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1920220447"/>
+        <c:axId val="915913423"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -677,12 +884,12 @@
             <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1920225727"/>
+        <c:crossAx val="915933583"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1920225727"/>
+        <c:axId val="915933583"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -739,7 +946,7 @@
             <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1920220447"/>
+        <c:crossAx val="915913423"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -753,6 +960,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -760,7 +968,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -795,7 +1002,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="es-ES"/>
@@ -810,6 +1017,36 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Absorbancia</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t>  vs concentración</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -848,6 +1085,17 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Azul!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>A</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
@@ -872,9 +1120,60 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="2"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.1837503509680741"/>
+                  <c:y val="-3.539821912581574E-4"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="es-PE"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Hoja3!$A$2:$A$6</c:f>
+              <c:f>Azul!$A$2:$A$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -898,18 +1197,24 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Hoja3!$B$2:$B$6</c:f>
+              <c:f>Azul!$B$2:$B$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>0.28999999999999998</c:v>
+                  <c:v>0.28000000000000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.27</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.31</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.41</c:v>
+                  <c:v>0.48</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.44</c:v>
+                  <c:v>0.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -917,7 +1222,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-77F3-481F-AA8F-8214CA42AA57}"/>
+              <c16:uniqueId val="{00000000-0D5A-4AE7-A454-1F3D284625CC}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -929,11 +1234,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1040982991"/>
-        <c:axId val="1040983471"/>
+        <c:axId val="957436575"/>
+        <c:axId val="957437055"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1040982991"/>
+        <c:axId val="957436575"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -990,12 +1295,12 @@
             <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1040983471"/>
+        <c:crossAx val="957437055"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1040983471"/>
+        <c:axId val="957437055"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1052,7 +1357,7 @@
             <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1040982991"/>
+        <c:crossAx val="957436575"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1066,6 +1371,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1073,7 +1379,2945 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-PE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-PE"/>
+              <a:t>Concentración vs Absorbancia</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-PE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Azul!$B$27</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Concentración</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="2"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.25539553669780912"/>
+                  <c:y val="2.6838495188101486E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="es-PE"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Azul!$A$28:$A$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.28000000000000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.27</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.31</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.48</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Azul!$B$28:$B$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7F9B-4F11-8993-1CF82062B273}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="957373215"/>
+        <c:axId val="957381855"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="957373215"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-PE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="957381855"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="957381855"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-PE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="957373215"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-PE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-PE"/>
+              <a:t>Absorbancia</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="es-PE" baseline="0"/>
+              <a:t> vs Concentración</a:t>
+            </a:r>
+            <a:endParaRPr lang="es-PE"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-PE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Verde!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>A</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="2"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="8.8480443666516417E-2"/>
+                  <c:y val="0.27989691491163904"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="es-PE"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Verde!$A$2:$A$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Verde!$B$2:$B$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.49</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.1499999999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.32</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4D59-41DD-9A84-01B40DB59979}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="957424575"/>
+        <c:axId val="957426015"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="957424575"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-PE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="957426015"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="957426015"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-PE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="957424575"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-PE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-PE"/>
+              <a:t>Concentración</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="es-PE" baseline="0"/>
+              <a:t> vs Absorbancia</a:t>
+            </a:r>
+            <a:endParaRPr lang="es-PE"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-PE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Verde!$B$30</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Concentración</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="2"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-9.4575021872265963E-2"/>
+                  <c:y val="9.0842811315252259E-4"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="es-PE"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Verde!$A$31:$A$35</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.49</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.1499999999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.32</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Verde!$B$31:$B$35</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B7DC-4617-9A98-6377C9C3A2EC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="957375615"/>
+        <c:axId val="957390015"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="957375615"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-PE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="957390015"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="957390015"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-PE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="957375615"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-PE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-PE" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Concentración vs Absorbancia</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-PE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Verde!$N$30</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Concentración</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.10235279965004375"/>
+                  <c:y val="8.9858559346748319E-4"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="es-PE"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Verde!$M$31:$M$35</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.49</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.1499999999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.32</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Verde!$N$31:$N$35</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6761-44FB-8451-2A15F2482543}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="329805695"/>
+        <c:axId val="329807615"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="329805695"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-PE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="329807615"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="329807615"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-PE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="329805695"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-PE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+              <a:lnSpc>
+                <a:spcPct val="100000"/>
+              </a:lnSpc>
+              <a:spcBef>
+                <a:spcPts val="0"/>
+              </a:spcBef>
+              <a:spcAft>
+                <a:spcPts val="0"/>
+              </a:spcAft>
+              <a:buClrTx/>
+              <a:buSzTx/>
+              <a:buFontTx/>
+              <a:buNone/>
+              <a:tabLst/>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Absorbancia  vs concentración</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-PE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Azul v2'!$L$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>A</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.15957422999768009"/>
+                  <c:y val="-5.1676702176933764E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="es-PE"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Azul v2'!$K$2:$K$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Azul v2'!$L$2:$L$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.56000000000000005</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.24</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.97</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.52</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-8595-4AF3-8D7C-BA406690CA9D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="957396735"/>
+        <c:axId val="957393855"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="957396735"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-PE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="957393855"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="957393855"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-PE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="957396735"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-PE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Absorbancia</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t>  vs concentración</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Azul v2'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>A</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="2"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.1837503509680741"/>
+                  <c:y val="-3.539821912581574E-4"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="es-PE"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Azul v2'!$A$2:$A$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Azul v2'!$B$2:$B$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.56000000000000005</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.24</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.97</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.52</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-1D5C-44F4-85A4-DD3623160E5E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="957436575"/>
+        <c:axId val="957437055"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="957436575"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-PE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="957437055"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="957437055"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-PE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="957436575"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-PE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-PE"/>
+              <a:t>Concentración vs Absorbancia</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-PE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Azul v2'!$B$27</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Concentración</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="2"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.25539553669780912"/>
+                  <c:y val="2.6838495188101486E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="es-PE"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Azul v2'!$A$28:$A$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.56000000000000005</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.24</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.97</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.52</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Azul v2'!$B$28:$B$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-421B-4DC5-957D-F547DDCC0A0A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="957373215"/>
+        <c:axId val="957381855"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="957373215"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-PE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="957381855"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="957381855"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-PE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="957373215"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1109,6 +4353,46 @@
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors10.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1228,6 +4512,246 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -1744,7 +5268,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style10.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -2260,7 +5784,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -2776,27 +6300,3639 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>87630</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>752474</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>579120</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>167640</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>761999</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Gráfico 2">
+        <xdr:cNvPr id="2" name="Gráfico 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5BF4FE70-2117-D662-F2BE-E465517F2AD5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E11D6DBF-4DB5-0C4F-208F-E0CE17B50BF2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2814,6 +9950,78 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>914399</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>190499</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Gráfico 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{263E29F8-4C6E-11F6-B178-0829116D980A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>895349</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>171449</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>9524</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Gráfico 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0183FE25-C429-9A06-40FB-6E7CD1FFBA06}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2821,23 +10029,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>320046</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>148590</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>404812</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>176212</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>137166</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>148590</xdr:rowOff>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Gráfico 1">
+        <xdr:cNvPr id="3" name="Gráfico 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2B2667B-159B-6A15-8C6F-FDC73A232DD7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E9980C8-BFE0-A170-D784-1F3379FDF53C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2855,30 +10063,25 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>354330</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
+      <xdr:colOff>747711</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>752474</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Gráfico 2">
+        <xdr:cNvPr id="4" name="Gráfico 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6F5878A-632B-8335-2EE6-36E0410E0A4A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC007CD5-8FA9-A59E-ADD6-D1AE7D086EA2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2890,7 +10093,198 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>223836</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>9524</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>19049</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>19049</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Gráfico 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D02CDE61-C54A-C92C-4617-062C2A5C784E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>752474</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>761999</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{665A4458-64BE-457B-8D2B-5F91624EB1DF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>914399</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>190499</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5AB3C8B6-D372-404F-AD7B-7F5ED8550E21}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>895349</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>171449</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>9524</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Gráfico 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9133BC9B-6968-4DBC-9238-EC719A449299}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>14286</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>19049</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Gráfico 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A1132ED-EE31-E490-A208-6C19A70FE14A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3196,55 +10590,144 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AE9CBE7-6585-4289-8B2D-526E6B212CDB}">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:L32"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="K1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0.1</v>
       </c>
       <c r="B2">
         <v>0.28000000000000003</v>
       </c>
+      <c r="K2">
+        <v>0.1</v>
+      </c>
+      <c r="L2">
+        <v>0.28000000000000003</v>
+      </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>0.25</v>
       </c>
       <c r="B3">
         <v>0.27</v>
       </c>
+      <c r="K3">
+        <v>0.25</v>
+      </c>
+      <c r="L3">
+        <v>0.27</v>
+      </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>0.5</v>
       </c>
       <c r="B4">
         <v>0.31</v>
       </c>
+      <c r="K4">
+        <v>0.5</v>
+      </c>
+      <c r="L4">
+        <v>0.31</v>
+      </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>0.75</v>
       </c>
       <c r="B5">
         <v>0.48</v>
       </c>
+      <c r="K5">
+        <v>0.75</v>
+      </c>
+      <c r="L5">
+        <v>0.48</v>
+      </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1</v>
       </c>
       <c r="B6">
         <v>0.7</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" s="2"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="B28">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>0.31</v>
+      </c>
+      <c r="B30">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>0.48</v>
+      </c>
+      <c r="B31">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>0.7</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3255,52 +10738,143 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B6B16E7-8219-4EAC-9D99-046412ADDC57}">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:N35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B1" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0.1</v>
       </c>
       <c r="B2">
-        <v>0.61</v>
+        <v>0.3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>0.25</v>
       </c>
       <c r="B3">
-        <v>1.1100000000000001</v>
+        <v>0.49</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>0.5</v>
       </c>
       <c r="B4">
-        <v>1.68</v>
+        <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>0.75</v>
       </c>
       <c r="B5">
-        <v>1.83</v>
+        <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1</v>
       </c>
       <c r="B6">
-        <v>1.94</v>
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>0.3</v>
+      </c>
+      <c r="B31">
+        <v>0.1</v>
+      </c>
+      <c r="M31">
+        <v>0.3</v>
+      </c>
+      <c r="N31">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>0.49</v>
+      </c>
+      <c r="B32">
+        <v>0.25</v>
+      </c>
+      <c r="M32">
+        <v>0.49</v>
+      </c>
+      <c r="N32">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>0.9</v>
+      </c>
+      <c r="B33">
+        <v>0.5</v>
+      </c>
+      <c r="M33">
+        <v>0.9</v>
+      </c>
+      <c r="N33">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="B34">
+        <v>0.75</v>
+      </c>
+      <c r="M34">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="N34">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>1.32</v>
+      </c>
+      <c r="B35">
+        <v>1</v>
+      </c>
+      <c r="M35">
+        <v>1.32</v>
+      </c>
+      <c r="N35">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3310,42 +10884,181 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87898E3C-D6C6-4342-AA6E-FB32897588C2}">
-  <dimension ref="A2:B6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7558A5B-B37A-49DC-96ED-EBFF7F065A4E}">
+  <dimension ref="A1:L32"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0.1</v>
       </c>
       <c r="B2">
-        <v>0.28999999999999998</v>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="K2">
+        <v>0.1</v>
+      </c>
+      <c r="L2">
+        <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>0.25</v>
       </c>
+      <c r="B3">
+        <v>1.24</v>
+      </c>
+      <c r="K3">
+        <v>0.25</v>
+      </c>
+      <c r="L3">
+        <v>1.24</v>
+      </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>0.5</v>
       </c>
+      <c r="B4">
+        <v>1.97</v>
+      </c>
+      <c r="K4">
+        <v>0.5</v>
+      </c>
+      <c r="L4">
+        <v>1.97</v>
+      </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>0.75</v>
       </c>
       <c r="B5">
-        <v>0.41</v>
+        <v>2.25</v>
+      </c>
+      <c r="K5">
+        <v>0.75</v>
+      </c>
+      <c r="L5">
+        <v>2.25</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1</v>
       </c>
       <c r="B6">
-        <v>0.44</v>
+        <v>2.52</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>2.52</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="J27" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="B28">
+        <v>0.1</v>
+      </c>
+      <c r="J28">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="K28">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>1.24</v>
+      </c>
+      <c r="B29">
+        <v>0.25</v>
+      </c>
+      <c r="J29">
+        <v>1.24</v>
+      </c>
+      <c r="K29">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>1.97</v>
+      </c>
+      <c r="B30">
+        <v>0.5</v>
+      </c>
+      <c r="J30">
+        <v>1.97</v>
+      </c>
+      <c r="K30">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>2.25</v>
+      </c>
+      <c r="B31">
+        <v>0.75</v>
+      </c>
+      <c r="J31">
+        <v>2.25</v>
+      </c>
+      <c r="K31">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>2.52</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="J32">
+        <v>2.52</v>
+      </c>
+      <c r="K32">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
